--- a/data/OP2/case33_3/case33_operational_data.xlsx
+++ b/data/OP2/case33_3/case33_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case33/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case33_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD14971-C9FD-3A41-AB76-C66F37970140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F14E64B-A422-CD47-BBD5-CCFBC2383CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="680" windowWidth="28400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,10 +454,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.1</v>
+        <f>E2*0.8</f>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="C2" s="1">
-        <v>0.06</v>
+        <f>F2*0.8</f>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="D2" s="2">
         <f>B2/SUM(B$2:B$33)</f>
@@ -475,14 +477,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.09</v>
+        <f t="shared" ref="B3:B33" si="0">E3*0.8</f>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C3" s="1">
-        <v>0.04</v>
+        <f t="shared" ref="C3:C33" si="1">F3*0.8</f>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D33" si="0">B3/SUM(B$2:B$33)</f>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" ref="D3:D33" si="2">B3/SUM(B$2:B$33)</f>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E3">
         <v>0.09</v>
@@ -496,13 +500,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0.12</v>
+        <f t="shared" si="0"/>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="C4" s="1">
-        <v>0.08</v>
+        <f t="shared" si="1"/>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E4">
@@ -517,13 +523,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C5" s="1">
-        <v>0.03</v>
+        <f t="shared" si="1"/>
+        <v>2.4E-2</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E5">
@@ -538,13 +546,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C6" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E6">
@@ -559,13 +569,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="C7" s="1">
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E7">
@@ -580,13 +592,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="C8" s="1">
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E8">
@@ -601,13 +615,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C9" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E9">
@@ -622,13 +638,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E10">
@@ -643,14 +661,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>4.4999999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="C11" s="1">
-        <v>0.03</v>
+        <f t="shared" si="1"/>
+        <v>2.4E-2</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>1.2113055181695823E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.2113055181695821E-2</v>
       </c>
       <c r="E11">
         <v>4.4999999999999998E-2</v>
@@ -664,13 +684,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C12" s="1">
-        <v>3.5000000000000003E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000004E-2</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E12">
@@ -685,13 +707,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C13" s="1">
-        <v>3.5000000000000003E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000004E-2</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E13">
@@ -706,13 +730,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>0.12</v>
+        <f t="shared" si="0"/>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="C14" s="1">
-        <v>0.08</v>
+        <f t="shared" si="1"/>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E14">
@@ -727,13 +753,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>0.01</v>
+        <f t="shared" si="1"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E15">
@@ -748,13 +776,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E16">
@@ -769,13 +799,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E17">
@@ -790,14 +822,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C18" s="1">
-        <v>0.04</v>
+        <f t="shared" si="1"/>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E18">
         <v>0.09</v>
@@ -811,14 +845,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C19" s="1">
-        <v>0.04</v>
+        <f t="shared" si="1"/>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E19">
         <v>0.09</v>
@@ -832,14 +868,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C20" s="1">
-        <v>0.04</v>
+        <f t="shared" si="1"/>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E20">
         <v>0.09</v>
@@ -853,14 +891,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C21" s="1">
-        <v>0.04</v>
+        <f t="shared" si="1"/>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E21">
         <v>0.09</v>
@@ -874,14 +914,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C22" s="1">
-        <v>0.04</v>
+        <f t="shared" si="1"/>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E22">
         <v>0.09</v>
@@ -895,14 +937,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C23" s="1">
-        <v>0.05</v>
+        <f t="shared" si="1"/>
+        <v>4.0000000000000008E-2</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4226110363391642E-2</v>
       </c>
       <c r="E23">
         <v>0.09</v>
@@ -916,14 +960,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>0.42</v>
+        <f t="shared" si="0"/>
+        <v>0.33600000000000002</v>
       </c>
       <c r="C24" s="1">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>0.11305518169582769</v>
+        <f t="shared" si="2"/>
+        <v>0.11305518169582768</v>
       </c>
       <c r="E24">
         <v>0.42</v>
@@ -937,14 +983,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>0.42</v>
+        <f t="shared" si="0"/>
+        <v>0.33600000000000002</v>
       </c>
       <c r="C25" s="1">
-        <v>0.2</v>
+        <f t="shared" si="1"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="0"/>
-        <v>0.11305518169582769</v>
+        <f t="shared" si="2"/>
+        <v>0.11305518169582768</v>
       </c>
       <c r="E25">
         <v>0.42</v>
@@ -958,13 +1006,15 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C26" s="1">
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E26">
@@ -979,13 +1029,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C27" s="1">
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E27">
@@ -1000,13 +1052,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C28" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E28">
@@ -1021,13 +1075,15 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>0.12</v>
+        <f t="shared" si="0"/>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="C29" s="1">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000008E-2</v>
       </c>
       <c r="D29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E29">
@@ -1042,13 +1098,15 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.16000000000000003</v>
       </c>
       <c r="C30" s="1">
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.48</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E30">
@@ -1063,13 +1121,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>0.15</v>
+        <f t="shared" si="0"/>
+        <v>0.12</v>
       </c>
       <c r="C31" s="1">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000008E-2</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.0376850605652742E-2</v>
       </c>
       <c r="E31">
@@ -1084,14 +1144,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>0.21</v>
+        <f t="shared" si="0"/>
+        <v>0.16800000000000001</v>
       </c>
       <c r="C32" s="1">
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" si="0"/>
-        <v>5.6527590847913846E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.6527590847913839E-2</v>
       </c>
       <c r="E32">
         <v>0.21</v>
@@ -1105,13 +1167,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>0.06</v>
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="C33" s="1">
-        <v>0.04</v>
+        <f t="shared" si="1"/>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E33">
